--- a/data_input/monthly/2026-06.xlsx
+++ b/data_input/monthly/2026-06.xlsx
@@ -16,19 +16,20 @@
     <sheet name="fact_promo_day" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="fact_lto_line" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="fact_partner" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="booking" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="ads_month" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="ads_brand" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="ads_objective" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="ads_campaign_detail" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="store_month" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="daily" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="coverage" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="dim_target" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="oa" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="cogs_cov" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="voucher_month" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="voucher_join" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="daily_party" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="booking" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="ads_month" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="ads_brand" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="ads_objective" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="ads_campaign_detail" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="store_month" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="daily" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="coverage" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="dim_target" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="oa" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="cogs_cov" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="voucher_month" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="voucher_join" sheetId="23" state="visible" r:id="rId23"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -472,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A78"/>
+  <dimension ref="A1:A80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="118" customWidth="1" min="1" max="1"/>
@@ -778,215 +779,229 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   booking                    6 dòng   bắt buộc: month, status</t>
+          <t xml:space="preserve">   daily_party               51 dòng   bắt buộc: date, store, net, tc</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  Booking tiệc &amp; sự kiện — gộp theo tháng NHẬN LEAD (month) × tháng DIỄN RA (ev_month) × cửa hàng × phân khúc × loại × nguồn × trạng thái. month = Inquiry Date → Input Date → (thiếu cả hai) ngày sự kiện, khi đó inq_est đếm số lead bị ước. seg ∈ event|table, stage ∈ won|open|lost — luật ở $booking. exp chỉ cộng ô có số (exp_n lead); ô trống/TBA KHÔNG tính là 0. closed_n = số lead Confirmed đã nhập Closed Revenue.</t>
+          <t xml:space="preserve">                                  Phần KHÁCH TIỆC của `daily`: chỉ các hoá đơn có Số khách ≥ $guest_segment.party_min_guests, gộp theo NGÀY × cửa hàng. ETL tự sinh từ bảng kê hoá đơn (S02). Khách lẻ = daily − daily_party.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   ads_month                  1 dòng   bắt buộc: month</t>
+          <t xml:space="preserve">   booking                    6 dòng   bắt buộc: month, status</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  Meta Ads tổng theo tháng. CHỈ cộng dòng cấp campaign — cộng cả adset là nhân đôi.</t>
+          <t xml:space="preserve">                                  Booking tiệc &amp; sự kiện — gộp theo tháng NHẬN LEAD (month) × tháng DIỄN RA (ev_month) × cửa hàng × phân khúc × loại × nguồn × trạng thái. month = Inquiry Date → Input Date → (thiếu cả hai) ngày sự kiện, khi đó inq_est đếm số lead bị ước. seg ∈ event|table, stage ∈ won|open|lost — luật ở $booking. exp chỉ cộng ô có số (exp_n lead); ô trống/TBA KHÔNG tính là 0. closed_n = số lead Confirmed đã nhập Closed Revenue.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   ads_brand                  3 dòng   bắt buộc: month, brand</t>
+          <t xml:space="preserve">   ads_month                  1 dòng   bắt buộc: month</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  Meta Ads theo brand. Nhãn `Tuyển dụng` không phải marketing thương hiệu.</t>
+          <t xml:space="preserve">                                  Meta Ads tổng theo tháng. CHỈ cộng dòng cấp campaign — cộng cả adset là nhân đôi.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   ads_objective              3 dòng   bắt buộc: month, objective</t>
+          <t xml:space="preserve">   ads_brand                  3 dòng   bắt buộc: month, brand</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  Meta Ads theo mục tiêu chiến dịch.</t>
+          <t xml:space="preserve">                                  Meta Ads theo brand. Nhãn `Tuyển dụng` không phải marketing thương hiệu.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   ads_campaign_detail       19 dòng   bắt buộc: month, brand, objective, campaign</t>
+          <t xml:space="preserve">   ads_objective              3 dòng   bắt buộc: month, objective</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  Chi tiết từng chiến dịch Meta trong tháng. page = mã fanpage đầu tên chiến dịch · rkind = loại kết quả chuẩn hoá · funnel = 'booking' nếu thuộc phễu booking tiệc (luật $booking.ads).</t>
+          <t xml:space="preserve">                                  Meta Ads theo mục tiêu chiến dịch.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  loader tự tính: cpr</t>
+          <t xml:space="preserve">   ads_campaign_detail       19 dòng   bắt buộc: month, brand, objective, campaign</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   store_month                9 dòng   bắt buộc: month, store, net, guest, tc</t>
+          <t xml:space="preserve">                                  Chi tiết từng chiến dịch Meta trong tháng. page = mã fanpage đầu tên chiến dịch · rkind = loại kết quả chuẩn hoá · funnel = 'booking' nếu thuộc phễu booking tiệc (luật $booking.ads).</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  XƯƠNG SỐNG của hệ thống. net = doanh thu thuần · guest = số khách · tc = số hoá đơn.</t>
+          <t xml:space="preserve">                                  loader tự tính: cpr</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  loader tự tính: ta, aov, brand, tier</t>
+          <t xml:space="preserve">   store_month                9 dòng   bắt buộc: month, store, net, guest, tc</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   daily                    248 dòng   bắt buộc: date, store, net</t>
+          <t xml:space="preserve">                                  XƯƠNG SỐNG của hệ thống. net = doanh thu thuần · guest = số khách · tc = số hoá đơn.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  Doanh thu theo NGÀY × cửa hàng. Ngày phải nằm trong tháng của file.</t>
+          <t xml:space="preserve">                                  loader tự tính: ta, aov, brand, tier</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   coverage                   1 dòng   bắt buộc: month</t>
+          <t xml:space="preserve">   daily                    248 dòng   bắt buộc: date, store, net</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  Số ngày THỰC CÓ dữ liệu — nhận diện tháng chưa trọn kỳ. Không khai thì loader suy từ daily.</t>
+          <t xml:space="preserve">                                  Doanh thu theo NGÀY × cửa hàng. Ngày phải nằm trong tháng của file.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  loader tự tính: partial</t>
+          <t xml:space="preserve">   coverage                   1 dòng   bắt buộc: month</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   dim_target                 5 dòng   bắt buộc: month, store, target</t>
+          <t xml:space="preserve">                                  Số ngày THỰC CÓ dữ liệu — nhận diện tháng chưa trọn kỳ. Không khai thì loader suy từ daily.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  Target doanh thu theo cửa hàng × tháng. Được phép khai cả tháng tương lai.</t>
+          <t xml:space="preserve">                                  loader tự tính: partial</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   oa                         1 dòng   bắt buộc: month</t>
+          <t xml:space="preserve">   dim_target                 5 dòng   bắt buộc: month, store, target</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  Zalo OA. follows = Quan tâm · views = Xem trang thông tin OA · menu = Tương tác thanh menu · content = Xem nội dung.</t>
+          <t xml:space="preserve">                                  Target doanh thu theo cửa hàng × tháng. Được phép khai cả tháng tương lai.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   cogs_cov                   1 dòng   bắt buộc: month</t>
+          <t xml:space="preserve">   oa                         1 dòng   bắt buộc: month</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  Độ phủ giá vốn theo tháng.</t>
+          <t xml:space="preserve">                                  Zalo OA. follows = Quan tâm · views = Xem trang thông tin OA · menu = Tương tác thanh menu · content = Xem nội dung.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  loader tự tính: pct</t>
+          <t xml:space="preserve">   cogs_cov                   1 dòng   bắt buộc: month</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   voucher_month              3 dòng   bắt buộc: m, brand</t>
+          <t xml:space="preserve">                                  Độ phủ giá vốn theo tháng.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  Voucher đã dùng theo tháng × brand.</t>
+          <t xml:space="preserve">                                  loader tự tính: pct</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   voucher_join               1 dòng   bắt buộc: m</t>
+          <t xml:space="preserve">   voucher_month              3 dòng   bắt buộc: m, brand</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  Tỷ lệ voucher khớp được với hoá đơn trong cùng tháng.</t>
+          <t xml:space="preserve">                                  Voucher đã dùng theo tháng × brand.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   voucher_join               1 dòng   bắt buộc: m</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                                  Tỷ lệ voucher khớp được với hoá đơn trong cùng tháng.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">                                  loader tự tính: rate</t>
         </is>
@@ -998,6 +1013,1125 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E52"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>store</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>net</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>844200</v>
+      </c>
+      <c r="D2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>NCB_MET</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>247000</v>
+      </c>
+      <c r="D3" t="n">
+        <v>22</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>13325000</v>
+      </c>
+      <c r="D4" t="n">
+        <v>40</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>NCB_MET</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>338000</v>
+      </c>
+      <c r="D5" t="n">
+        <v>34</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>10169397</v>
+      </c>
+      <c r="D6" t="n">
+        <v>14</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>4414662</v>
+      </c>
+      <c r="D7" t="n">
+        <v>15</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>NJFB_CRE</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>7214792</v>
+      </c>
+      <c r="D8" t="n">
+        <v>10</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>907800</v>
+      </c>
+      <c r="D9" t="n">
+        <v>17</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>NCB_SKC</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>652000</v>
+      </c>
+      <c r="D10" t="n">
+        <v>10</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>NJFB_CRE</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>3103443</v>
+      </c>
+      <c r="D11" t="n">
+        <v>10</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>NCB_MET</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>286000</v>
+      </c>
+      <c r="D12" t="n">
+        <v>44</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>1246000</v>
+      </c>
+      <c r="D13" t="n">
+        <v>10</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>NJFB_CRE</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>22754939</v>
+      </c>
+      <c r="D14" t="n">
+        <v>41</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>NCB_MET</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>128000</v>
+      </c>
+      <c r="D15" t="n">
+        <v>22</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>NJFB_CRE</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>9740388</v>
+      </c>
+      <c r="D16" t="n">
+        <v>11</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>NCB_MET</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>437000</v>
+      </c>
+      <c r="D17" t="n">
+        <v>12</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>16297596</v>
+      </c>
+      <c r="D18" t="n">
+        <v>30</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1637000</v>
+      </c>
+      <c r="D19" t="n">
+        <v>10</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>NCB_SKC</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>188000</v>
+      </c>
+      <c r="D20" t="n">
+        <v>11</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>4226650</v>
+      </c>
+      <c r="D21" t="n">
+        <v>26</v>
+      </c>
+      <c r="E21" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>NCB_MET</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>4808000</v>
+      </c>
+      <c r="D22" t="n">
+        <v>21</v>
+      </c>
+      <c r="E22" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>964005</v>
+      </c>
+      <c r="D23" t="n">
+        <v>10</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>NCB_SKC</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>701000</v>
+      </c>
+      <c r="D24" t="n">
+        <v>12</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>NCB_MET</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>207000</v>
+      </c>
+      <c r="D25" t="n">
+        <v>21</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>11451000</v>
+      </c>
+      <c r="D26" t="n">
+        <v>59</v>
+      </c>
+      <c r="E26" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>10465686</v>
+      </c>
+      <c r="D27" t="n">
+        <v>11</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>NJFB_CRE</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>3993608</v>
+      </c>
+      <c r="D28" t="n">
+        <v>10</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>5857110</v>
+      </c>
+      <c r="D29" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>NJFB_CRE</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>5867600</v>
+      </c>
+      <c r="D30" t="n">
+        <v>10</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>NCB_SKC</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>910000</v>
+      </c>
+      <c r="D31" t="n">
+        <v>10</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>NJFB_CRE</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>26362892</v>
+      </c>
+      <c r="D32" t="n">
+        <v>12</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>NJFB_CRE</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>7703829</v>
+      </c>
+      <c r="D33" t="n">
+        <v>14</v>
+      </c>
+      <c r="E33" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>409500</v>
+      </c>
+      <c r="D34" t="n">
+        <v>16</v>
+      </c>
+      <c r="E34" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>4046792</v>
+      </c>
+      <c r="D35" t="n">
+        <v>10</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>NJFB_SSV</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>4755996</v>
+      </c>
+      <c r="D36" t="n">
+        <v>17</v>
+      </c>
+      <c r="E36" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>NCB_MET</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>228000</v>
+      </c>
+      <c r="D37" t="n">
+        <v>11</v>
+      </c>
+      <c r="E37" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>NJFB_SSV</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>8350774</v>
+      </c>
+      <c r="D38" t="n">
+        <v>12</v>
+      </c>
+      <c r="E38" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>198000</v>
+      </c>
+      <c r="D39" t="n">
+        <v>22</v>
+      </c>
+      <c r="E39" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>NCB_SKC</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>79000</v>
+      </c>
+      <c r="D40" t="n">
+        <v>10</v>
+      </c>
+      <c r="E40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>183646074</v>
+      </c>
+      <c r="D41" t="n">
+        <v>74</v>
+      </c>
+      <c r="E41" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>NCB_MET</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>1107000</v>
+      </c>
+      <c r="D42" t="n">
+        <v>12</v>
+      </c>
+      <c r="E42" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>NCB_SKC</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>2065000</v>
+      </c>
+      <c r="D43" t="n">
+        <v>10</v>
+      </c>
+      <c r="E43" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>8854272</v>
+      </c>
+      <c r="D44" t="n">
+        <v>40</v>
+      </c>
+      <c r="E44" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>NJFB_CRE</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>9521915</v>
+      </c>
+      <c r="D45" t="n">
+        <v>22</v>
+      </c>
+      <c r="E45" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>NCB_SKC</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>1007000</v>
+      </c>
+      <c r="D46" t="n">
+        <v>10</v>
+      </c>
+      <c r="E46" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>672462</v>
+      </c>
+      <c r="D47" t="n">
+        <v>11</v>
+      </c>
+      <c r="E47" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>9086410</v>
+      </c>
+      <c r="D48" t="n">
+        <v>30</v>
+      </c>
+      <c r="E48" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>4646000</v>
+      </c>
+      <c r="D49" t="n">
+        <v>55</v>
+      </c>
+      <c r="E49" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>NCB_NDC</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>870750</v>
+      </c>
+      <c r="D50" t="n">
+        <v>13</v>
+      </c>
+      <c r="E50" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>5409747</v>
+      </c>
+      <c r="D51" t="n">
+        <v>16</v>
+      </c>
+      <c r="E51" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>NJFB_SSV</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>7254912</v>
+      </c>
+      <c r="D52" t="n">
+        <v>15</v>
+      </c>
+      <c r="E52" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1561,7 +2695,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1628,7 +2762,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1724,7 +2858,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1820,7 +2954,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2768,7 +3902,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3071,7 +4205,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8327,7 +9461,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8398,7 +9532,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8502,91 +9636,6 @@
       </c>
       <c r="C6" t="n">
         <v>2945250000</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>month</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>follows</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>msgs</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>views</t>
-        </is>
-      </c>
-      <c r="E1" s="4" t="inlineStr">
-        <is>
-          <t>menu</t>
-        </is>
-      </c>
-      <c r="F1" s="4" t="inlineStr">
-        <is>
-          <t>content</t>
-        </is>
-      </c>
-      <c r="G1" s="4" t="inlineStr">
-        <is>
-          <t>days</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>7</v>
-      </c>
-      <c r="C2" t="n">
-        <v>7</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26</v>
-      </c>
-      <c r="E2" t="n">
-        <v>44</v>
-      </c>
-      <c r="F2" t="n">
-        <v>50</v>
-      </c>
-      <c r="G2" t="n">
-        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -8753,38 +9802,52 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>month</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
-        <is>
-          <t>rev</t>
-        </is>
-      </c>
-      <c r="C1" s="5" t="inlineStr">
-        <is>
-          <t>rev_cov</t>
-        </is>
-      </c>
-      <c r="D1" s="5" t="inlineStr">
-        <is>
-          <t>sku</t>
-        </is>
-      </c>
-      <c r="E1" s="5" t="inlineStr">
-        <is>
-          <t>sku_cov</t>
-        </is>
-      </c>
-      <c r="F1" s="5" t="inlineStr">
-        <is>
-          <t>pct</t>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>follows</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>msgs</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>views</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>menu</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>content</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>days</t>
         </is>
       </c>
     </row>
@@ -8795,19 +9858,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4968949071</v>
+        <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>2091815000</v>
+        <v>7</v>
       </c>
       <c r="D2" t="n">
-        <v>659</v>
+        <v>26</v>
       </c>
       <c r="E2" t="n">
-        <v>160</v>
+        <v>44</v>
       </c>
       <c r="F2" t="n">
-        <v>0.421</v>
+        <v>50</v>
+      </c>
+      <c r="G2" t="n">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -8821,33 +9887,38 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>month</t>
         </is>
       </c>
       <c r="B1" s="5" t="inlineStr">
         <is>
-          <t>brand</t>
+          <t>rev</t>
         </is>
       </c>
       <c r="C1" s="5" t="inlineStr">
         <is>
-          <t>used</t>
+          <t>rev_cov</t>
         </is>
       </c>
       <c r="D1" s="5" t="inlineStr">
         <is>
-          <t>rev</t>
+          <t>sku</t>
         </is>
       </c>
       <c r="E1" s="5" t="inlineStr">
         <is>
-          <t>disc</t>
+          <t>sku_cov</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>pct</t>
         </is>
       </c>
     </row>
@@ -8857,61 +9928,20 @@
           <t>2026-06</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>NCB</t>
-        </is>
+      <c r="B2" t="n">
+        <v>4968949071</v>
       </c>
       <c r="C2" t="n">
-        <v>131</v>
+        <v>2091815000</v>
       </c>
       <c r="D2" t="n">
-        <v>25324000</v>
+        <v>659</v>
       </c>
       <c r="E2" t="n">
-        <v>5064800</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>NDC</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>6</v>
-      </c>
-      <c r="D3" t="n">
-        <v>2207000</v>
-      </c>
-      <c r="E3" t="n">
-        <v>441400</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>NJFB</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>11874000</v>
-      </c>
-      <c r="E4" t="n">
-        <v>2338800</v>
+        <v>160</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.421</v>
       </c>
     </row>
   </sheetData>
@@ -8920,6 +9950,110 @@
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>brand</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>used</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>rev</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>disc</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>NCB</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>131</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25324000</v>
+      </c>
+      <c r="E2" t="n">
+        <v>5064800</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>NDC</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2207000</v>
+      </c>
+      <c r="E3" t="n">
+        <v>441400</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>NJFB</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>11874000</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2338800</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
